--- a/BOM/GTV3_Board/PCBWay-BOM.xlsx
+++ b/BOM/GTV3_Board/PCBWay-BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="537">
   <si>
     <t>Component list</t>
   </si>
@@ -2122,15 +2122,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2204,6 +2195,15 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2574,11 +2574,11 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
     </row>
     <row r="2" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2603,31 +2603,31 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="15"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50" t="s">
+      <c r="C3" s="46"/>
+      <c r="D3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="50"/>
-      <c r="F3" s="51" t="s">
+      <c r="E3" s="47"/>
+      <c r="F3" s="48" t="s">
         <v>536</v>
       </c>
-      <c r="G3" s="50"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="34"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="62"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50" t="s">
+      <c r="C4" s="46"/>
+      <c r="D4" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="50"/>
+      <c r="E4" s="47"/>
       <c r="F4" s="31" t="s">
         <v>536</v>
       </c>
@@ -2638,16 +2638,16 @@
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="35"/>
+      <c r="N4" s="63"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="15"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50" t="s">
+      <c r="C5" s="46"/>
+      <c r="D5" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="50"/>
+      <c r="E5" s="47"/>
       <c r="F5" s="32" t="s">
         <v>5</v>
       </c>
@@ -2658,7 +2658,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="35"/>
+      <c r="N5" s="63"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2674,39 +2674,39 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="35"/>
+      <c r="N6" s="63"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="17"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="35"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="63"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="19"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="35"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="63"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2722,7 +2722,7 @@
       <c r="E9" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="33" t="s">
         <v>193</v>
       </c>
       <c r="G9" s="20" t="s">
@@ -2756,7 +2756,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="22" t="s">
@@ -2787,7 +2787,7 @@
         <f>K10*5</f>
         <v>65</v>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="44">
         <v>80</v>
       </c>
       <c r="N10" s="22"/>
@@ -2798,7 +2798,7 @@
         <f t="shared" ref="B11:B105" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="35" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="24" t="s">
@@ -2840,13 +2840,13 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>409</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="36" t="s">
         <v>110</v>
       </c>
       <c r="F12" s="23" t="s">
@@ -2871,7 +2871,7 @@
         <f>K12*5</f>
         <v>45</v>
       </c>
-      <c r="M12" s="47">
+      <c r="M12" s="44">
         <v>100</v>
       </c>
       <c r="N12" s="22"/>
@@ -2882,7 +2882,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="35" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="24" t="s">
@@ -2924,13 +2924,13 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>410</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="36" t="s">
         <v>112</v>
       </c>
       <c r="F14" s="23" t="s">
@@ -2955,7 +2955,7 @@
         <f>K14*5</f>
         <v>185</v>
       </c>
-      <c r="M14" s="47">
+      <c r="M14" s="44">
         <v>200</v>
       </c>
       <c r="N14" s="22"/>
@@ -2966,7 +2966,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="35" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="24" t="s">
@@ -3008,13 +3008,13 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="36" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="23" t="s">
@@ -3039,7 +3039,7 @@
         <f>K16*5</f>
         <v>5</v>
       </c>
-      <c r="M16" s="47">
+      <c r="M16" s="44">
         <v>100</v>
       </c>
       <c r="N16" s="22"/>
@@ -3050,7 +3050,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="35" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="24" t="s">
@@ -3092,13 +3092,13 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="36" t="s">
         <v>116</v>
       </c>
       <c r="F18" s="23" t="s">
@@ -3123,7 +3123,7 @@
         <f>K18*5</f>
         <v>10</v>
       </c>
-      <c r="M18" s="47">
+      <c r="M18" s="44">
         <v>100</v>
       </c>
       <c r="N18" s="22"/>
@@ -3134,7 +3134,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="35" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="24" t="s">
@@ -3176,13 +3176,13 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="36" t="s">
         <v>118</v>
       </c>
       <c r="F20" s="23" t="s">
@@ -3207,7 +3207,7 @@
         <f>K20*5</f>
         <v>5</v>
       </c>
-      <c r="M20" s="47">
+      <c r="M20" s="44">
         <v>20</v>
       </c>
       <c r="N20" s="22"/>
@@ -3218,7 +3218,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="35" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="24" t="s">
@@ -3260,13 +3260,13 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="39" t="s">
+      <c r="E22" s="36" t="s">
         <v>120</v>
       </c>
       <c r="F22" s="23" t="s">
@@ -3291,7 +3291,7 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="M22" s="47">
+      <c r="M22" s="44">
         <v>100</v>
       </c>
       <c r="N22" s="22"/>
@@ -3302,7 +3302,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="35" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="24" t="s">
@@ -3344,13 +3344,13 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="36" t="s">
         <v>122</v>
       </c>
       <c r="F24" s="23" t="s">
@@ -3375,7 +3375,7 @@
         <f t="shared" ref="L24" si="7">K24*5</f>
         <v>5</v>
       </c>
-      <c r="M24" s="47">
+      <c r="M24" s="44">
         <v>100</v>
       </c>
       <c r="N24" s="22"/>
@@ -3386,7 +3386,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="24" t="s">
@@ -3428,13 +3428,13 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="39" t="s">
+      <c r="E26" s="36" t="s">
         <v>124</v>
       </c>
       <c r="F26" s="23" t="s">
@@ -3459,7 +3459,7 @@
         <f t="shared" ref="L26" si="8">K26*5</f>
         <v>5</v>
       </c>
-      <c r="M26" s="47">
+      <c r="M26" s="44">
         <v>6</v>
       </c>
       <c r="N26" s="22"/>
@@ -3470,7 +3470,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="24" t="s">
@@ -3512,13 +3512,13 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="39" t="s">
+      <c r="E28" s="36" t="s">
         <v>126</v>
       </c>
       <c r="F28" s="23" t="s">
@@ -3543,7 +3543,7 @@
         <f t="shared" ref="L28" si="9">K28*5</f>
         <v>25</v>
       </c>
-      <c r="M28" s="47">
+      <c r="M28" s="44">
         <v>40</v>
       </c>
       <c r="N28" s="22"/>
@@ -3554,7 +3554,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="24" t="s">
@@ -3596,13 +3596,13 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E30" s="39" t="s">
+      <c r="E30" s="36" t="s">
         <v>128</v>
       </c>
       <c r="F30" s="23" t="s">
@@ -3627,7 +3627,7 @@
         <f t="shared" ref="L30" si="10">K30*5</f>
         <v>5</v>
       </c>
-      <c r="M30" s="47">
+      <c r="M30" s="44">
         <v>10</v>
       </c>
       <c r="N30" s="22"/>
@@ -3638,7 +3638,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="24" t="s">
@@ -3680,13 +3680,13 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="37" t="s">
+      <c r="C32" s="34" t="s">
         <v>412</v>
       </c>
       <c r="D32" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="39" t="s">
+      <c r="E32" s="36" t="s">
         <v>130</v>
       </c>
       <c r="F32" s="23" t="s">
@@ -3711,7 +3711,7 @@
         <f t="shared" ref="L32" si="11">K32*5</f>
         <v>5</v>
       </c>
-      <c r="M32" s="47">
+      <c r="M32" s="44">
         <v>10</v>
       </c>
       <c r="N32" s="22"/>
@@ -3722,41 +3722,43 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="C33" s="35" t="s">
         <v>414</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F33" s="25" t="s">
+      <c r="F33" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="G33" s="24" t="s">
+      <c r="G33" s="37" t="s">
         <v>526</v>
       </c>
-      <c r="H33" s="25" t="s">
+      <c r="H33" s="42" t="s">
         <v>313</v>
       </c>
-      <c r="I33" s="24" t="s">
+      <c r="I33" s="37" t="s">
         <v>464</v>
       </c>
-      <c r="J33" s="24" t="s">
+      <c r="J33" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="K33" s="25">
+      <c r="K33" s="42">
         <v>9</v>
       </c>
-      <c r="L33" s="24">
+      <c r="L33" s="37">
         <f>K33*5</f>
         <v>45</v>
       </c>
-      <c r="M33" s="25">
+      <c r="M33" s="45">
         <v>50</v>
       </c>
-      <c r="N33" s="24"/>
+      <c r="N33" s="60" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="34" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -3764,41 +3766,43 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="37" t="s">
+      <c r="C34" s="34" t="s">
         <v>414</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="39" t="s">
+      <c r="E34" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F34" s="23" t="s">
+      <c r="F34" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="37" t="s">
         <v>527</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="42" t="s">
         <v>313</v>
       </c>
-      <c r="I34" s="22" t="s">
+      <c r="I34" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="J34" s="22" t="s">
+      <c r="J34" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="K34" s="23">
+      <c r="K34" s="42">
         <v>5</v>
       </c>
-      <c r="L34" s="22">
+      <c r="L34" s="37">
         <f t="shared" ref="L34" si="12">K34*5</f>
         <v>25</v>
       </c>
-      <c r="M34" s="47">
+      <c r="M34" s="45">
         <v>30</v>
       </c>
-      <c r="N34" s="22"/>
+      <c r="N34" s="58" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="35" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
@@ -3806,7 +3810,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="38" t="s">
+      <c r="C35" s="35" t="s">
         <v>414</v>
       </c>
       <c r="D35" s="24" t="s">
@@ -3848,41 +3852,41 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="C36" s="34" t="s">
         <v>415</v>
       </c>
-      <c r="D36" s="40" t="s">
+      <c r="D36" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="40" t="s">
+      <c r="E36" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="F36" s="45" t="s">
+      <c r="F36" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="G36" s="40" t="s">
+      <c r="G36" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="H36" s="45" t="s">
+      <c r="H36" s="42" t="s">
         <v>314</v>
       </c>
-      <c r="I36" s="40" t="s">
+      <c r="I36" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="J36" s="40" t="s">
+      <c r="J36" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="K36" s="45">
+      <c r="K36" s="42">
         <v>1</v>
       </c>
-      <c r="L36" s="40">
+      <c r="L36" s="37">
         <f t="shared" ref="L36" si="13">K36*5</f>
         <v>5</v>
       </c>
-      <c r="M36" s="48">
+      <c r="M36" s="45">
         <v>6</v>
       </c>
-      <c r="N36" s="62" t="s">
+      <c r="N36" s="59" t="s">
         <v>524</v>
       </c>
     </row>
@@ -3892,41 +3896,43 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="38" t="s">
+      <c r="C37" s="35" t="s">
         <v>412</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="F37" s="25" t="s">
+      <c r="F37" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="G37" s="24" t="s">
+      <c r="G37" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="H37" s="25" t="s">
+      <c r="H37" s="42" t="s">
         <v>416</v>
       </c>
-      <c r="I37" s="24" t="s">
+      <c r="I37" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="J37" s="24" t="s">
+      <c r="J37" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="K37" s="25">
+      <c r="K37" s="42">
         <v>1</v>
       </c>
-      <c r="L37" s="24">
+      <c r="L37" s="37">
         <f>K37*5</f>
         <v>5</v>
       </c>
-      <c r="M37" s="25">
+      <c r="M37" s="45">
         <v>10</v>
       </c>
-      <c r="N37" s="24"/>
+      <c r="N37" s="59" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="38" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
@@ -3934,13 +3940,13 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C38" s="34" t="s">
         <v>9</v>
       </c>
       <c r="D38" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="39" t="s">
+      <c r="E38" s="36" t="s">
         <v>134</v>
       </c>
       <c r="F38" s="23" t="s">
@@ -3965,7 +3971,7 @@
         <f t="shared" ref="L38" si="14">K38*5</f>
         <v>5</v>
       </c>
-      <c r="M38" s="47">
+      <c r="M38" s="44">
         <v>6</v>
       </c>
       <c r="N38" s="22"/>
@@ -3976,41 +3982,43 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="38" t="s">
+      <c r="C39" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="24" t="s">
+      <c r="D39" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F39" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="G39" s="24" t="s">
+      <c r="G39" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="H39" s="25" t="s">
+      <c r="H39" s="42" t="s">
         <v>315</v>
       </c>
-      <c r="I39" s="24" t="s">
+      <c r="I39" s="37" t="s">
         <v>353</v>
       </c>
-      <c r="J39" s="24" t="s">
+      <c r="J39" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="42">
         <v>5</v>
       </c>
-      <c r="L39" s="24">
+      <c r="L39" s="37">
         <f>K39*5</f>
         <v>25</v>
       </c>
-      <c r="M39" s="25">
+      <c r="M39" s="45">
         <v>27</v>
       </c>
-      <c r="N39" s="24"/>
+      <c r="N39" s="59" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="40" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
@@ -4018,13 +4026,13 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="37" t="s">
+      <c r="C40" s="34" t="s">
         <v>417</v>
       </c>
       <c r="D40" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="39" t="s">
+      <c r="E40" s="36" t="s">
         <v>136</v>
       </c>
       <c r="F40" s="23" t="s">
@@ -4049,7 +4057,7 @@
         <f t="shared" ref="L40" si="15">K40*5</f>
         <v>5</v>
       </c>
-      <c r="M40" s="47">
+      <c r="M40" s="44">
         <v>10</v>
       </c>
       <c r="N40" s="22"/>
@@ -4060,7 +4068,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="35" t="s">
         <v>417</v>
       </c>
       <c r="D41" s="24" t="s">
@@ -4102,13 +4110,13 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="37" t="s">
+      <c r="C42" s="34" t="s">
         <v>417</v>
       </c>
       <c r="D42" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E42" s="39" t="s">
+      <c r="E42" s="36" t="s">
         <v>138</v>
       </c>
       <c r="F42" s="23" t="s">
@@ -4133,7 +4141,7 @@
         <f t="shared" ref="L42" si="16">K42*5</f>
         <v>5</v>
       </c>
-      <c r="M42" s="47">
+      <c r="M42" s="44">
         <v>10</v>
       </c>
       <c r="N42" s="22"/>
@@ -4144,7 +4152,7 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="38" t="s">
+      <c r="C43" s="35" t="s">
         <v>417</v>
       </c>
       <c r="D43" s="24" t="s">
@@ -4186,13 +4194,13 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="37" t="s">
+      <c r="C44" s="34" t="s">
         <v>418</v>
       </c>
       <c r="D44" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E44" s="39" t="s">
+      <c r="E44" s="36" t="s">
         <v>140</v>
       </c>
       <c r="F44" s="23" t="s">
@@ -4217,7 +4225,7 @@
         <f t="shared" ref="L44" si="17">K44*5</f>
         <v>35</v>
       </c>
-      <c r="M44" s="47">
+      <c r="M44" s="44">
         <v>40</v>
       </c>
       <c r="N44" s="22"/>
@@ -4228,7 +4236,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="38" t="s">
+      <c r="C45" s="35" t="s">
         <v>418</v>
       </c>
       <c r="D45" s="24" t="s">
@@ -4270,13 +4278,13 @@
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="37" t="s">
+      <c r="C46" s="34" t="s">
         <v>419</v>
       </c>
       <c r="D46" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E46" s="39" t="s">
+      <c r="E46" s="36" t="s">
         <v>142</v>
       </c>
       <c r="F46" s="23" t="s">
@@ -4301,7 +4309,7 @@
         <f t="shared" ref="L46" si="18">K46*5</f>
         <v>5</v>
       </c>
-      <c r="M46" s="47">
+      <c r="M46" s="44">
         <v>10</v>
       </c>
       <c r="N46" s="22"/>
@@ -4312,41 +4320,41 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="C47" s="39" t="s">
         <v>378</v>
       </c>
-      <c r="D47" s="41" t="s">
+      <c r="D47" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="E47" s="41" t="s">
+      <c r="E47" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="F47" s="43" t="s">
+      <c r="F47" s="40" t="s">
         <v>407</v>
       </c>
-      <c r="G47" s="41" t="s">
+      <c r="G47" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="H47" s="43" t="s">
+      <c r="H47" s="40" t="s">
         <v>420</v>
       </c>
-      <c r="I47" s="41" t="s">
+      <c r="I47" s="38" t="s">
         <v>420</v>
       </c>
-      <c r="J47" s="41" t="s">
+      <c r="J47" s="38" t="s">
         <v>420</v>
       </c>
-      <c r="K47" s="43">
+      <c r="K47" s="40">
         <v>2</v>
       </c>
-      <c r="L47" s="41">
+      <c r="L47" s="38">
         <f>K47*5</f>
         <v>10</v>
       </c>
-      <c r="M47" s="43" t="s">
+      <c r="M47" s="40" t="s">
         <v>420</v>
       </c>
-      <c r="N47" s="63" t="s">
+      <c r="N47" s="60" t="s">
         <v>524</v>
       </c>
     </row>
@@ -4356,41 +4364,43 @@
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="37" t="s">
+      <c r="C48" s="34" t="s">
         <v>412</v>
       </c>
-      <c r="D48" s="22" t="s">
+      <c r="D48" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="39" t="s">
+      <c r="E48" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="F48" s="23" t="s">
+      <c r="F48" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="G48" s="22" t="s">
+      <c r="G48" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="H48" s="23" t="s">
+      <c r="H48" s="40" t="s">
         <v>323</v>
       </c>
-      <c r="I48" s="22" t="s">
+      <c r="I48" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="J48" s="22" t="s">
+      <c r="J48" s="38" t="s">
         <v>420</v>
       </c>
-      <c r="K48" s="23">
+      <c r="K48" s="40">
         <v>2</v>
       </c>
-      <c r="L48" s="22">
+      <c r="L48" s="38">
         <f t="shared" ref="L48" si="19">K48*5</f>
         <v>10</v>
       </c>
-      <c r="M48" s="47">
+      <c r="M48" s="40">
         <v>50</v>
       </c>
-      <c r="N48" s="22"/>
+      <c r="N48" s="60" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="49" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
@@ -4398,41 +4408,43 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="38" t="s">
+      <c r="C49" s="35" t="s">
         <v>412</v>
       </c>
-      <c r="D49" s="24" t="s">
+      <c r="D49" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="E49" s="24" t="s">
+      <c r="E49" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="F49" s="25" t="s">
+      <c r="F49" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="G49" s="24" t="s">
+      <c r="G49" s="38" t="s">
         <v>530</v>
       </c>
-      <c r="H49" s="25" t="s">
+      <c r="H49" s="40" t="s">
         <v>323</v>
       </c>
-      <c r="I49" s="24" t="s">
+      <c r="I49" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="J49" s="24" t="s">
+      <c r="J49" s="38" t="s">
         <v>420</v>
       </c>
-      <c r="K49" s="25">
+      <c r="K49" s="40">
         <v>4</v>
       </c>
-      <c r="L49" s="24">
+      <c r="L49" s="38">
         <f>K49*5</f>
         <v>20</v>
       </c>
-      <c r="M49" s="25">
+      <c r="M49" s="40">
         <v>40</v>
       </c>
-      <c r="N49" s="24"/>
+      <c r="N49" s="60" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="50" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
@@ -4440,41 +4452,43 @@
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="37" t="s">
+      <c r="C50" s="34" t="s">
         <v>412</v>
       </c>
-      <c r="D50" s="22" t="s">
+      <c r="D50" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="E50" s="39" t="s">
+      <c r="E50" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="F50" s="23" t="s">
+      <c r="F50" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="G50" s="22" t="s">
+      <c r="G50" s="38" t="s">
         <v>478</v>
       </c>
-      <c r="H50" s="23" t="s">
+      <c r="H50" s="40" t="s">
         <v>324</v>
       </c>
-      <c r="I50" s="22" t="s">
+      <c r="I50" s="38" t="s">
         <v>478</v>
       </c>
-      <c r="J50" s="22" t="s">
+      <c r="J50" s="38" t="s">
         <v>420</v>
       </c>
-      <c r="K50" s="23">
+      <c r="K50" s="40">
         <v>1</v>
       </c>
-      <c r="L50" s="22">
+      <c r="L50" s="38">
         <f t="shared" ref="L50" si="20">K50*5</f>
         <v>5</v>
       </c>
-      <c r="M50" s="47">
+      <c r="M50" s="40">
         <v>10</v>
       </c>
-      <c r="N50" s="22"/>
+      <c r="N50" s="60" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="51" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
@@ -4482,41 +4496,43 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="38" t="s">
+      <c r="C51" s="35" t="s">
         <v>412</v>
       </c>
-      <c r="D51" s="24" t="s">
+      <c r="D51" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E51" s="24" t="s">
+      <c r="E51" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="F51" s="25" t="s">
+      <c r="F51" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="G51" s="24" t="s">
+      <c r="G51" s="38" t="s">
         <v>531</v>
       </c>
-      <c r="H51" s="25" t="s">
+      <c r="H51" s="40" t="s">
         <v>323</v>
       </c>
-      <c r="I51" s="24" t="s">
+      <c r="I51" s="38" t="s">
         <v>479</v>
       </c>
-      <c r="J51" s="24" t="s">
+      <c r="J51" s="38" t="s">
         <v>420</v>
       </c>
-      <c r="K51" s="25">
+      <c r="K51" s="40">
         <v>3</v>
       </c>
-      <c r="L51" s="24">
+      <c r="L51" s="38">
         <f>K51*5</f>
         <v>15</v>
       </c>
-      <c r="M51" s="25">
+      <c r="M51" s="40">
         <v>50</v>
       </c>
-      <c r="N51" s="24"/>
+      <c r="N51" s="60" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="52" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -4524,41 +4540,43 @@
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="37" t="s">
+      <c r="C52" s="34" t="s">
         <v>412</v>
       </c>
-      <c r="D52" s="22" t="s">
+      <c r="D52" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E52" s="39" t="s">
+      <c r="E52" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="F52" s="23" t="s">
+      <c r="F52" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="G52" s="22" t="s">
+      <c r="G52" s="38" t="s">
         <v>532</v>
       </c>
-      <c r="H52" s="23" t="s">
+      <c r="H52" s="40" t="s">
         <v>323</v>
       </c>
-      <c r="I52" s="22" t="s">
+      <c r="I52" s="38" t="s">
         <v>480</v>
       </c>
-      <c r="J52" s="22" t="s">
+      <c r="J52" s="38" t="s">
         <v>420</v>
       </c>
-      <c r="K52" s="23">
+      <c r="K52" s="40">
         <v>1</v>
       </c>
-      <c r="L52" s="22">
+      <c r="L52" s="38">
         <f t="shared" ref="L52" si="21">K52*5</f>
         <v>5</v>
       </c>
-      <c r="M52" s="47">
+      <c r="M52" s="40">
         <v>20</v>
       </c>
-      <c r="N52" s="22"/>
+      <c r="N52" s="60" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="53" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
@@ -4566,7 +4584,7 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="38" t="s">
+      <c r="C53" s="35" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="24" t="s">
@@ -4608,13 +4626,13 @@
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="37" t="s">
+      <c r="C54" s="34" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E54" s="39" t="s">
+      <c r="E54" s="36" t="s">
         <v>150</v>
       </c>
       <c r="F54" s="23" t="s">
@@ -4639,7 +4657,7 @@
         <f t="shared" ref="L54" si="22">K54*5</f>
         <v>5</v>
       </c>
-      <c r="M54" s="47">
+      <c r="M54" s="44">
         <v>10</v>
       </c>
       <c r="N54" s="22"/>
@@ -4650,7 +4668,7 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="38" t="s">
+      <c r="C55" s="35" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="24" t="s">
@@ -4692,13 +4710,13 @@
         <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
-      <c r="C56" s="37" t="s">
+      <c r="C56" s="34" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="E56" s="39" t="s">
+      <c r="E56" s="36" t="s">
         <v>152</v>
       </c>
       <c r="F56" s="23" t="s">
@@ -4723,7 +4741,7 @@
         <f t="shared" ref="L56" si="23">K56*5</f>
         <v>10</v>
       </c>
-      <c r="M56" s="47">
+      <c r="M56" s="44">
         <v>15</v>
       </c>
       <c r="N56" s="22"/>
@@ -4734,7 +4752,7 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="38" t="s">
+      <c r="C57" s="35" t="s">
         <v>11</v>
       </c>
       <c r="D57" s="24" t="s">
@@ -4776,13 +4794,13 @@
         <f>ROW(B58) - ROW($B$9)</f>
         <v>49</v>
       </c>
-      <c r="C58" s="37" t="s">
+      <c r="C58" s="34" t="s">
         <v>11</v>
       </c>
       <c r="D58" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="E58" s="39" t="s">
+      <c r="E58" s="36" t="s">
         <v>154</v>
       </c>
       <c r="F58" s="23" t="s">
@@ -4807,7 +4825,7 @@
         <f t="shared" ref="L58" si="24">K58*5</f>
         <v>50</v>
       </c>
-      <c r="M58" s="47">
+      <c r="M58" s="44">
         <v>60</v>
       </c>
       <c r="N58" s="22"/>
@@ -4818,7 +4836,7 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="38" t="s">
+      <c r="C59" s="35" t="s">
         <v>11</v>
       </c>
       <c r="D59" s="24" t="s">
@@ -4860,13 +4878,13 @@
         <f>ROW(B60) - ROW($B$9)</f>
         <v>51</v>
       </c>
-      <c r="C60" s="37" t="s">
+      <c r="C60" s="34" t="s">
         <v>11</v>
       </c>
       <c r="D60" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="E60" s="39" t="s">
+      <c r="E60" s="36" t="s">
         <v>156</v>
       </c>
       <c r="F60" s="23" t="s">
@@ -4891,7 +4909,7 @@
         <f t="shared" ref="L60" si="25">K60*5</f>
         <v>15</v>
       </c>
-      <c r="M60" s="47">
+      <c r="M60" s="44">
         <v>20</v>
       </c>
       <c r="N60" s="22"/>
@@ -4902,7 +4920,7 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="38" t="s">
+      <c r="C61" s="35" t="s">
         <v>11</v>
       </c>
       <c r="D61" s="24" t="s">
@@ -4944,13 +4962,13 @@
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="37" t="s">
+      <c r="C62" s="34" t="s">
         <v>11</v>
       </c>
       <c r="D62" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="E62" s="39" t="s">
+      <c r="E62" s="36" t="s">
         <v>158</v>
       </c>
       <c r="F62" s="23" t="s">
@@ -4975,7 +4993,7 @@
         <f t="shared" ref="L62" si="26">K62*5</f>
         <v>5</v>
       </c>
-      <c r="M62" s="47">
+      <c r="M62" s="44">
         <v>10</v>
       </c>
       <c r="N62" s="22"/>
@@ -4986,7 +5004,7 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="38" t="s">
+      <c r="C63" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D63" s="24" t="s">
@@ -5028,13 +5046,13 @@
         <f>ROW(B64) - ROW($B$9)</f>
         <v>55</v>
       </c>
-      <c r="C64" s="37" t="s">
+      <c r="C64" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D64" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="E64" s="39" t="s">
+      <c r="E64" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F64" s="23" t="s">
@@ -5059,7 +5077,7 @@
         <f t="shared" ref="L64" si="27">K64*5</f>
         <v>5</v>
       </c>
-      <c r="M64" s="47">
+      <c r="M64" s="44">
         <v>100</v>
       </c>
       <c r="N64" s="22"/>
@@ -5070,7 +5088,7 @@
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C65" s="38" t="s">
+      <c r="C65" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D65" s="24" t="s">
@@ -5112,13 +5130,13 @@
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="37" t="s">
+      <c r="C66" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D66" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="E66" s="39" t="s">
+      <c r="E66" s="36" t="s">
         <v>423</v>
       </c>
       <c r="F66" s="23" t="s">
@@ -5143,7 +5161,7 @@
         <f>K66*5</f>
         <v>75</v>
       </c>
-      <c r="M66" s="47">
+      <c r="M66" s="44">
         <v>100</v>
       </c>
       <c r="N66" s="22"/>
@@ -5154,7 +5172,7 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="38" t="s">
+      <c r="C67" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D67" s="24" t="s">
@@ -5196,13 +5214,13 @@
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
-      <c r="C68" s="37" t="s">
+      <c r="C68" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D68" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E68" s="39" t="s">
+      <c r="E68" s="36" t="s">
         <v>163</v>
       </c>
       <c r="F68" s="23" t="s">
@@ -5227,7 +5245,7 @@
         <f>K68*5</f>
         <v>5</v>
       </c>
-      <c r="M68" s="47">
+      <c r="M68" s="44">
         <v>100</v>
       </c>
       <c r="N68" s="22"/>
@@ -5238,7 +5256,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="38" t="s">
+      <c r="C69" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D69" s="24" t="s">
@@ -5280,13 +5298,13 @@
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
-      <c r="C70" s="37" t="s">
+      <c r="C70" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D70" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="E70" s="39" t="s">
+      <c r="E70" s="36" t="s">
         <v>164</v>
       </c>
       <c r="F70" s="23" t="s">
@@ -5311,7 +5329,7 @@
         <f>K70*5</f>
         <v>5</v>
       </c>
-      <c r="M70" s="47">
+      <c r="M70" s="44">
         <v>100</v>
       </c>
       <c r="N70" s="22"/>
@@ -5322,7 +5340,7 @@
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="38" t="s">
+      <c r="C71" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D71" s="24" t="s">
@@ -5364,13 +5382,13 @@
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
-      <c r="C72" s="37" t="s">
+      <c r="C72" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D72" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="E72" s="39" t="s">
+      <c r="E72" s="36" t="s">
         <v>426</v>
       </c>
       <c r="F72" s="23" t="s">
@@ -5395,7 +5413,7 @@
         <f>K72*5</f>
         <v>40</v>
       </c>
-      <c r="M72" s="47">
+      <c r="M72" s="44">
         <v>100</v>
       </c>
       <c r="N72" s="22"/>
@@ -5406,7 +5424,7 @@
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="38" t="s">
+      <c r="C73" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D73" s="24" t="s">
@@ -5448,13 +5466,13 @@
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="37" t="s">
+      <c r="C74" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D74" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="E74" s="39" t="s">
+      <c r="E74" s="36" t="s">
         <v>429</v>
       </c>
       <c r="F74" s="23" t="s">
@@ -5479,7 +5497,7 @@
         <f>K74*5</f>
         <v>65</v>
       </c>
-      <c r="M74" s="47">
+      <c r="M74" s="44">
         <v>100</v>
       </c>
       <c r="N74" s="22"/>
@@ -5490,7 +5508,7 @@
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="38" t="s">
+      <c r="C75" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D75" s="24" t="s">
@@ -5532,13 +5550,13 @@
         <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
-      <c r="C76" s="37" t="s">
+      <c r="C76" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E76" s="39" t="s">
+      <c r="E76" s="36" t="s">
         <v>167</v>
       </c>
       <c r="F76" s="23" t="s">
@@ -5563,7 +5581,7 @@
         <f>K76*5</f>
         <v>5</v>
       </c>
-      <c r="M76" s="47">
+      <c r="M76" s="44">
         <v>20</v>
       </c>
       <c r="N76" s="22"/>
@@ -5574,7 +5592,7 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C77" s="38" t="s">
+      <c r="C77" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="24" t="s">
@@ -5616,13 +5634,13 @@
         <f>ROW(B78) - ROW($B$9)</f>
         <v>69</v>
       </c>
-      <c r="C78" s="37" t="s">
+      <c r="C78" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D78" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="E78" s="39" t="s">
+      <c r="E78" s="36" t="s">
         <v>435</v>
       </c>
       <c r="F78" s="23" t="s">
@@ -5647,7 +5665,7 @@
         <f>K78*5</f>
         <v>120</v>
       </c>
-      <c r="M78" s="47">
+      <c r="M78" s="44">
         <v>200</v>
       </c>
       <c r="N78" s="22"/>
@@ -5658,7 +5676,7 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="38" t="s">
+      <c r="C79" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D79" s="24" t="s">
@@ -5700,13 +5718,13 @@
         <f>ROW(B80) - ROW($B$9)</f>
         <v>71</v>
       </c>
-      <c r="C80" s="37" t="s">
+      <c r="C80" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D80" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="E80" s="39" t="s">
+      <c r="E80" s="36" t="s">
         <v>169</v>
       </c>
       <c r="F80" s="23" t="s">
@@ -5731,7 +5749,7 @@
         <f>K80*5</f>
         <v>5</v>
       </c>
-      <c r="M80" s="47">
+      <c r="M80" s="44">
         <v>50</v>
       </c>
       <c r="N80" s="22"/>
@@ -5742,7 +5760,7 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="38" t="s">
+      <c r="C81" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D81" s="24" t="s">
@@ -5784,13 +5802,13 @@
         <f>ROW(B82) - ROW($B$9)</f>
         <v>73</v>
       </c>
-      <c r="C82" s="37" t="s">
+      <c r="C82" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D82" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="E82" s="39" t="s">
+      <c r="E82" s="36" t="s">
         <v>171</v>
       </c>
       <c r="F82" s="23" t="s">
@@ -5815,7 +5833,7 @@
         <f>K82*5</f>
         <v>10</v>
       </c>
-      <c r="M82" s="47">
+      <c r="M82" s="44">
         <v>100</v>
       </c>
       <c r="N82" s="22"/>
@@ -5826,7 +5844,7 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C83" s="38" t="s">
+      <c r="C83" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D83" s="24" t="s">
@@ -5868,13 +5886,13 @@
         <f>ROW(B84) - ROW($B$9)</f>
         <v>75</v>
       </c>
-      <c r="C84" s="37" t="s">
+      <c r="C84" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D84" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E84" s="39" t="s">
+      <c r="E84" s="36" t="s">
         <v>437</v>
       </c>
       <c r="F84" s="23" t="s">
@@ -5899,7 +5917,7 @@
         <f>K84*5</f>
         <v>10</v>
       </c>
-      <c r="M84" s="47">
+      <c r="M84" s="44">
         <v>100</v>
       </c>
       <c r="N84" s="22"/>
@@ -5910,7 +5928,7 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C85" s="38" t="s">
+      <c r="C85" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D85" s="24" t="s">
@@ -5952,13 +5970,13 @@
         <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
-      <c r="C86" s="37" t="s">
+      <c r="C86" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D86" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="E86" s="39" t="s">
+      <c r="E86" s="36" t="s">
         <v>174</v>
       </c>
       <c r="F86" s="23" t="s">
@@ -5983,7 +6001,7 @@
         <f>K86*5</f>
         <v>10</v>
       </c>
-      <c r="M86" s="47">
+      <c r="M86" s="44">
         <v>50</v>
       </c>
       <c r="N86" s="22"/>
@@ -5994,7 +6012,7 @@
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C87" s="38" t="s">
+      <c r="C87" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D87" s="24" t="s">
@@ -6036,13 +6054,13 @@
         <f>ROW(B88) - ROW($B$9)</f>
         <v>79</v>
       </c>
-      <c r="C88" s="37" t="s">
+      <c r="C88" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D88" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="E88" s="39" t="s">
+      <c r="E88" s="36" t="s">
         <v>175</v>
       </c>
       <c r="F88" s="23" t="s">
@@ -6067,7 +6085,7 @@
         <f>K88*5</f>
         <v>5</v>
       </c>
-      <c r="M88" s="47">
+      <c r="M88" s="44">
         <v>50</v>
       </c>
       <c r="N88" s="22"/>
@@ -6078,7 +6096,7 @@
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C89" s="38" t="s">
+      <c r="C89" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D89" s="24" t="s">
@@ -6120,41 +6138,41 @@
         <f>ROW(B90) - ROW($B$9)</f>
         <v>81</v>
       </c>
-      <c r="C90" s="44" t="s">
+      <c r="C90" s="41" t="s">
         <v>227</v>
       </c>
-      <c r="D90" s="40" t="s">
+      <c r="D90" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="E90" s="40" t="s">
+      <c r="E90" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="F90" s="45" t="s">
+      <c r="F90" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="G90" s="40" t="s">
+      <c r="G90" s="37" t="s">
         <v>227</v>
       </c>
-      <c r="H90" s="45" t="s">
+      <c r="H90" s="42" t="s">
         <v>420</v>
       </c>
-      <c r="I90" s="40" t="s">
+      <c r="I90" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="J90" s="40" t="s">
+      <c r="J90" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="K90" s="45">
+      <c r="K90" s="42">
         <v>42</v>
       </c>
-      <c r="L90" s="40">
+      <c r="L90" s="37">
         <f t="shared" si="39"/>
         <v>210</v>
       </c>
-      <c r="M90" s="48" t="s">
+      <c r="M90" s="45" t="s">
         <v>420</v>
       </c>
-      <c r="N90" s="61" t="s">
+      <c r="N90" s="58" t="s">
         <v>524</v>
       </c>
     </row>
@@ -6164,7 +6182,7 @@
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="C91" s="38" t="s">
+      <c r="C91" s="35" t="s">
         <v>440</v>
       </c>
       <c r="D91" s="24" t="s">
@@ -6206,13 +6224,13 @@
         <f>ROW(B92) - ROW($B$9)</f>
         <v>83</v>
       </c>
-      <c r="C92" s="37" t="s">
+      <c r="C92" s="34" t="s">
         <v>441</v>
       </c>
       <c r="D92" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="E92" s="39" t="s">
+      <c r="E92" s="36" t="s">
         <v>179</v>
       </c>
       <c r="F92" s="23" t="s">
@@ -6237,7 +6255,7 @@
         <f t="shared" ref="L92" si="40">K92*5</f>
         <v>10</v>
       </c>
-      <c r="M92" s="47">
+      <c r="M92" s="44">
         <v>11</v>
       </c>
       <c r="N92" s="22"/>
@@ -6248,7 +6266,7 @@
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="C93" s="38" t="s">
+      <c r="C93" s="35" t="s">
         <v>441</v>
       </c>
       <c r="D93" s="24" t="s">
@@ -6290,13 +6308,13 @@
         <f>ROW(B94) - ROW($B$9)</f>
         <v>85</v>
       </c>
-      <c r="C94" s="37" t="s">
+      <c r="C94" s="34" t="s">
         <v>441</v>
       </c>
       <c r="D94" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E94" s="39" t="s">
+      <c r="E94" s="36" t="s">
         <v>181</v>
       </c>
       <c r="F94" s="23" t="s">
@@ -6321,7 +6339,7 @@
         <f t="shared" ref="L94" si="41">K94*5</f>
         <v>5</v>
       </c>
-      <c r="M94" s="47">
+      <c r="M94" s="44">
         <v>6</v>
       </c>
       <c r="N94" s="22"/>
@@ -6332,7 +6350,7 @@
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="C95" s="38" t="s">
+      <c r="C95" s="35" t="s">
         <v>441</v>
       </c>
       <c r="D95" s="24" t="s">
@@ -6374,13 +6392,13 @@
         <f>ROW(B96) - ROW($B$9)</f>
         <v>87</v>
       </c>
-      <c r="C96" s="37" t="s">
+      <c r="C96" s="34" t="s">
         <v>441</v>
       </c>
       <c r="D96" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="E96" s="39" t="s">
+      <c r="E96" s="36" t="s">
         <v>183</v>
       </c>
       <c r="F96" s="23" t="s">
@@ -6405,7 +6423,7 @@
         <f t="shared" ref="L96" si="42">K96*5</f>
         <v>5</v>
       </c>
-      <c r="M96" s="47">
+      <c r="M96" s="44">
         <v>6</v>
       </c>
       <c r="N96" s="22"/>
@@ -6416,7 +6434,7 @@
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="C97" s="38" t="s">
+      <c r="C97" s="35" t="s">
         <v>441</v>
       </c>
       <c r="D97" s="24" t="s">
@@ -6458,13 +6476,13 @@
         <f>ROW(B98) - ROW($B$9)</f>
         <v>89</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C98" s="34" t="s">
         <v>441</v>
       </c>
       <c r="D98" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="E98" s="39" t="s">
+      <c r="E98" s="36" t="s">
         <v>185</v>
       </c>
       <c r="F98" s="23" t="s">
@@ -6489,7 +6507,7 @@
         <f t="shared" ref="L98" si="43">K98*5</f>
         <v>20</v>
       </c>
-      <c r="M98" s="47">
+      <c r="M98" s="44">
         <v>25</v>
       </c>
       <c r="N98" s="22"/>
@@ -6500,7 +6518,7 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="C99" s="38" t="s">
+      <c r="C99" s="35" t="s">
         <v>441</v>
       </c>
       <c r="D99" s="24" t="s">
@@ -6542,13 +6560,13 @@
         <f>ROW(B100) - ROW($B$9)</f>
         <v>91</v>
       </c>
-      <c r="C100" s="37" t="s">
+      <c r="C100" s="34" t="s">
         <v>441</v>
       </c>
       <c r="D100" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="E100" s="39" t="s">
+      <c r="E100" s="36" t="s">
         <v>187</v>
       </c>
       <c r="F100" s="23" t="s">
@@ -6573,7 +6591,7 @@
         <f t="shared" ref="L100" si="44">K100*5</f>
         <v>5</v>
       </c>
-      <c r="M100" s="47">
+      <c r="M100" s="44">
         <v>6</v>
       </c>
       <c r="N100" s="22"/>
@@ -6584,7 +6602,7 @@
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="C101" s="38" t="s">
+      <c r="C101" s="35" t="s">
         <v>441</v>
       </c>
       <c r="D101" s="24" t="s">
@@ -6626,41 +6644,43 @@
         <f>ROW(B102) - ROW($B$9)</f>
         <v>93</v>
       </c>
-      <c r="C102" s="37" t="s">
+      <c r="C102" s="34" t="s">
         <v>441</v>
       </c>
-      <c r="D102" s="22" t="s">
+      <c r="D102" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="E102" s="39" t="s">
+      <c r="E102" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="F102" s="23" t="s">
+      <c r="F102" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="G102" s="22" t="s">
+      <c r="G102" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="H102" s="23" t="s">
+      <c r="H102" s="42" t="s">
         <v>340</v>
       </c>
-      <c r="I102" s="22" t="s">
+      <c r="I102" s="37" t="s">
         <v>519</v>
       </c>
-      <c r="J102" s="22" t="s">
+      <c r="J102" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="K102" s="23">
+      <c r="K102" s="42">
         <v>1</v>
       </c>
-      <c r="L102" s="22">
+      <c r="L102" s="37">
         <f t="shared" ref="L102" si="45">K102*5</f>
         <v>5</v>
       </c>
-      <c r="M102" s="47">
+      <c r="M102" s="45">
         <v>6</v>
       </c>
-      <c r="N102" s="22"/>
+      <c r="N102" s="59" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="103" spans="1:14" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
@@ -6668,7 +6688,7 @@
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="C103" s="38" t="s">
+      <c r="C103" s="35" t="s">
         <v>444</v>
       </c>
       <c r="D103" s="24" t="s">
@@ -6710,13 +6730,13 @@
         <f>ROW(B104) - ROW($B$9)</f>
         <v>95</v>
       </c>
-      <c r="C104" s="37" t="s">
+      <c r="C104" s="34" t="s">
         <v>444</v>
       </c>
       <c r="D104" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="E104" s="39" t="s">
+      <c r="E104" s="36" t="s">
         <v>191</v>
       </c>
       <c r="F104" s="23" t="s">
@@ -6741,7 +6761,7 @@
         <f t="shared" ref="L104" si="46">K104*5</f>
         <v>5</v>
       </c>
-      <c r="M104" s="47">
+      <c r="M104" s="44">
         <v>10</v>
       </c>
       <c r="N104" s="22"/>
@@ -6752,41 +6772,41 @@
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="C105" s="59" t="s">
+      <c r="C105" s="56" t="s">
         <v>444</v>
       </c>
-      <c r="D105" s="46" t="s">
+      <c r="D105" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="E105" s="46" t="s">
+      <c r="E105" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="F105" s="60" t="s">
+      <c r="F105" s="57" t="s">
         <v>407</v>
       </c>
-      <c r="G105" s="46" t="s">
+      <c r="G105" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="H105" s="60" t="s">
+      <c r="H105" s="57" t="s">
         <v>343</v>
       </c>
-      <c r="I105" s="46" t="s">
+      <c r="I105" s="43" t="s">
         <v>521</v>
       </c>
-      <c r="J105" s="46" t="s">
+      <c r="J105" s="43" t="s">
         <v>406</v>
       </c>
-      <c r="K105" s="60">
+      <c r="K105" s="57">
         <v>1</v>
       </c>
-      <c r="L105" s="46">
+      <c r="L105" s="43">
         <f>K105*5</f>
         <v>5</v>
       </c>
-      <c r="M105" s="60">
+      <c r="M105" s="57">
         <v>10</v>
       </c>
-      <c r="N105" s="46"/>
+      <c r="N105" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="2">
